--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_8.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03174720407281566</v>
+        <v>0.02319628644220849</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008444969144207771</v>
+        <v>0.008432213998538026</v>
       </c>
       <c r="C2" t="n">
-        <v>50503824</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50503824</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>33636048</v>
+        <v>4042820</v>
       </c>
       <c r="L2" t="n">
-        <v>17472410</v>
+        <v>1987505</v>
       </c>
       <c r="M2" t="n">
-        <v>3877882</v>
+        <v>421134</v>
       </c>
       <c r="N2" t="n">
-        <v>121878</v>
+        <v>12100</v>
       </c>
       <c r="O2" t="n">
-        <v>2358474</v>
+        <v>261498</v>
       </c>
       <c r="P2" t="n">
-        <v>935705</v>
+        <v>105069</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999951720237732</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8219341039657593</v>
+        <v>0.7846418619155884</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6571835875511169</v>
+        <v>0.5950733423233032</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5688084959983826</v>
+        <v>0.4929106533527374</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1559042632579803</v>
+        <v>0.1254016011953354</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6278131008148193</v>
+        <v>0.5566001534461975</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7385615110397339</v>
+        <v>0.671200156211853</v>
       </c>
       <c r="X2" t="n">
-        <v>50503824</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50503824</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>38435590</v>
+        <v>4813274</v>
       </c>
       <c r="AG2" t="n">
-        <v>23824653</v>
+        <v>3010697</v>
       </c>
       <c r="AH2" t="n">
-        <v>6405435</v>
+        <v>804213</v>
       </c>
       <c r="AI2" t="n">
-        <v>472232</v>
+        <v>59267</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3675525</v>
+        <v>460431</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9562234282493591</v>
+        <v>0.9555724859237671</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114547371864319</v>
+        <v>0.9118132591247559</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582150936126709</v>
+        <v>0.8582125902175903</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619678735733032</v>
+        <v>0.6612037420272827</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020171165466309</v>
+        <v>0.9019888043403625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.008211592150493557</v>
+        <v>0.005715125485924222</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002024809124862332</v>
+        <v>0.002020802637879015</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>33636048</v>
+        <v>4042820</v>
       </c>
       <c r="E3" t="n">
-        <v>6271128</v>
+        <v>942935</v>
       </c>
       <c r="F3" t="n">
-        <v>199512</v>
+        <v>35714</v>
       </c>
       <c r="G3" t="n">
-        <v>15420</v>
+        <v>2592</v>
       </c>
       <c r="H3" t="n">
-        <v>16465</v>
+        <v>2784</v>
       </c>
       <c r="I3" t="n">
-        <v>1380</v>
+        <v>192</v>
       </c>
       <c r="J3" t="n">
-        <v>80132732</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>83209827</v>
+        <v>10279341</v>
       </c>
       <c r="L3" t="n">
-        <v>95338543</v>
+        <v>11754065</v>
       </c>
       <c r="M3" t="n">
-        <v>120226311</v>
+        <v>15043975</v>
       </c>
       <c r="N3" t="n">
-        <v>129262870</v>
+        <v>16241836</v>
       </c>
       <c r="O3" t="n">
-        <v>125161484</v>
+        <v>15696752</v>
       </c>
       <c r="P3" t="n">
-        <v>128758454</v>
+        <v>16170940</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8379688858985901</v>
+        <v>0.8042149543762207</v>
       </c>
       <c r="S3" t="n">
-        <v>0.667296826839447</v>
+        <v>0.6005441546440125</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5190706253051758</v>
+        <v>0.4485985636711121</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1706833690404892</v>
+        <v>0.1347828954458237</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5784628391265869</v>
+        <v>0.5118048787117004</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6048036217689514</v>
+        <v>0.5427398085594177</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38435590</v>
+        <v>4813274</v>
       </c>
       <c r="Z3" t="n">
-        <v>1581425</v>
+        <v>198388</v>
       </c>
       <c r="AA3" t="n">
-        <v>68001</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>54459</v>
+        <v>6867</v>
       </c>
       <c r="AC3" t="n">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80132976</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>88737218</v>
+        <v>11165177</v>
       </c>
       <c r="AG3" t="n">
-        <v>102138438</v>
+        <v>12815311</v>
       </c>
       <c r="AH3" t="n">
-        <v>122107746</v>
+        <v>15344357</v>
       </c>
       <c r="AI3" t="n">
-        <v>129681597</v>
+        <v>16295858</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126160401</v>
+        <v>15855036</v>
       </c>
       <c r="AK3" t="n">
-        <v>128983636</v>
+        <v>16209148</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575390219688416</v>
+        <v>0.9574769735336304</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098982810974121</v>
+        <v>0.9097115993499756</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573940396308899</v>
+        <v>0.8566603064537048</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613346934318542</v>
+        <v>0.6601800322532654</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014958739280701</v>
+        <v>0.9011573195457458</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.07162734766631908</v>
+        <v>0.05836736562433582</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0319507024117701</v>
+        <v>0.03191057304788653</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6772927</v>
+        <v>1028950</v>
       </c>
       <c r="E4" t="n">
-        <v>17472410</v>
+        <v>1987505</v>
       </c>
       <c r="F4" t="n">
-        <v>1626334</v>
+        <v>239637</v>
       </c>
       <c r="G4" t="n">
-        <v>89620</v>
+        <v>14803</v>
       </c>
       <c r="H4" t="n">
-        <v>198956</v>
+        <v>34399</v>
       </c>
       <c r="I4" t="n">
-        <v>23614</v>
+        <v>4212</v>
       </c>
       <c r="J4" t="n">
-        <v>244</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>7287000</v>
+        <v>1109620</v>
       </c>
       <c r="L4" t="n">
-        <v>9114393</v>
+        <v>1352428</v>
       </c>
       <c r="M4" t="n">
-        <v>2939671</v>
+        <v>433248</v>
       </c>
       <c r="N4" t="n">
-        <v>659871</v>
+        <v>84390</v>
       </c>
       <c r="O4" t="n">
-        <v>1398176</v>
+        <v>208315</v>
       </c>
       <c r="P4" t="n">
-        <v>331224</v>
+        <v>51470</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999975562095642</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8298740386962891</v>
+        <v>0.7943078279495239</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6622015833854675</v>
+        <v>0.5977962613105774</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5428025126457214</v>
+        <v>0.4697118401527405</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1629594266414642</v>
+        <v>0.1299231201410294</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6021284461021423</v>
+        <v>0.5332634449005127</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6650234460830688</v>
+        <v>0.6001731157302856</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1643061</v>
+        <v>208961</v>
       </c>
       <c r="Z4" t="n">
-        <v>23824653</v>
+        <v>3010697</v>
       </c>
       <c r="AA4" t="n">
-        <v>662423</v>
+        <v>83070</v>
       </c>
       <c r="AB4" t="n">
-        <v>44064</v>
+        <v>5580</v>
       </c>
       <c r="AC4" t="n">
-        <v>9119</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1759609</v>
+        <v>223784</v>
       </c>
       <c r="AG4" t="n">
-        <v>2314498</v>
+        <v>291182</v>
       </c>
       <c r="AH4" t="n">
-        <v>1058236</v>
+        <v>132866</v>
       </c>
       <c r="AI4" t="n">
-        <v>241144</v>
+        <v>30368</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399259</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568807482719421</v>
+        <v>0.9565237760543823</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106758832931519</v>
+        <v>0.9107611775398254</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578044176101685</v>
+        <v>0.8574357628822327</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616511344909668</v>
+        <v>0.660691499710083</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017564058303833</v>
+        <v>0.9015728235244751</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>365298</v>
+        <v>58989</v>
       </c>
       <c r="E5" t="n">
-        <v>2329397</v>
+        <v>325876</v>
       </c>
       <c r="F5" t="n">
-        <v>3877882</v>
+        <v>421134</v>
       </c>
       <c r="G5" t="n">
-        <v>214742</v>
+        <v>27871</v>
       </c>
       <c r="H5" t="n">
-        <v>609349</v>
+        <v>92265</v>
       </c>
       <c r="I5" t="n">
-        <v>74136</v>
+        <v>12640</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6503925</v>
+        <v>984219</v>
       </c>
       <c r="L5" t="n">
-        <v>8711454</v>
+        <v>1322002</v>
       </c>
       <c r="M5" t="n">
-        <v>3592936</v>
+        <v>517643</v>
       </c>
       <c r="N5" t="n">
-        <v>592181</v>
+        <v>77674</v>
       </c>
       <c r="O5" t="n">
-        <v>1718666</v>
+        <v>249435</v>
       </c>
       <c r="P5" t="n">
-        <v>611417</v>
+        <v>88521</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.999998152256012</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8944330811500549</v>
+        <v>0.8724513053894043</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8635464906692505</v>
+        <v>0.8370839357376099</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9499941468238831</v>
+        <v>0.9420753717422485</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9904157519340515</v>
+        <v>0.9901276826858521</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9761411547660828</v>
+        <v>0.9721156358718872</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9927842617034912</v>
+        <v>0.9914723038673401</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64236</v>
+        <v>8176</v>
       </c>
       <c r="Z5" t="n">
-        <v>683114</v>
+        <v>86508</v>
       </c>
       <c r="AA5" t="n">
-        <v>6405435</v>
+        <v>804213</v>
       </c>
       <c r="AB5" t="n">
-        <v>79701</v>
+        <v>10008</v>
       </c>
       <c r="AC5" t="n">
-        <v>233268</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1704383</v>
+        <v>213765</v>
       </c>
       <c r="AG5" t="n">
-        <v>2359211</v>
+        <v>298810</v>
       </c>
       <c r="AH5" t="n">
-        <v>1065383</v>
+        <v>134564</v>
       </c>
       <c r="AI5" t="n">
-        <v>241827</v>
+        <v>30507</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401615</v>
+        <v>50502</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734838008880615</v>
+        <v>0.9733461737632751</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642236232757568</v>
+        <v>0.9640599489212036</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837440848350525</v>
+        <v>0.9837091565132141</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963029623031616</v>
+        <v>0.9962917566299438</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938694834709167</v>
+        <v>0.9938759207725525</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983740448951721</v>
+        <v>0.9983792304992676</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>119189</v>
+        <v>16588</v>
       </c>
       <c r="E6" t="n">
-        <v>173023</v>
+        <v>23526</v>
       </c>
       <c r="F6" t="n">
-        <v>207931</v>
+        <v>24879</v>
       </c>
       <c r="G6" t="n">
-        <v>121878</v>
+        <v>12100</v>
       </c>
       <c r="H6" t="n">
-        <v>81987</v>
+        <v>11060</v>
       </c>
       <c r="I6" t="n">
-        <v>10001</v>
+        <v>1614</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>51905</v>
+        <v>6591</v>
       </c>
       <c r="Z6" t="n">
-        <v>42831</v>
+        <v>5395</v>
       </c>
       <c r="AA6" t="n">
-        <v>87352</v>
+        <v>11026</v>
       </c>
       <c r="AB6" t="n">
-        <v>472232</v>
+        <v>59267</v>
       </c>
       <c r="AC6" t="n">
-        <v>55891</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>28474</v>
+        <v>5008</v>
       </c>
       <c r="E7" t="n">
-        <v>312275</v>
+        <v>54859</v>
       </c>
       <c r="F7" t="n">
-        <v>841057</v>
+        <v>121768</v>
       </c>
       <c r="G7" t="n">
-        <v>314713</v>
+        <v>34987</v>
       </c>
       <c r="H7" t="n">
-        <v>2358474</v>
+        <v>261498</v>
       </c>
       <c r="I7" t="n">
-        <v>222093</v>
+        <v>32812</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>6480</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237812</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60794</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3675525</v>
+        <v>460431</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>103</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>1112</v>
+        <v>85</v>
       </c>
       <c r="E8" t="n">
-        <v>28570</v>
+        <v>5232</v>
       </c>
       <c r="F8" t="n">
-        <v>64837</v>
+        <v>11250</v>
       </c>
       <c r="G8" t="n">
-        <v>25376</v>
+        <v>4137</v>
       </c>
       <c r="H8" t="n">
-        <v>491419</v>
+        <v>67807</v>
       </c>
       <c r="I8" t="n">
-        <v>935705</v>
+        <v>105069</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
